--- a/artfynd/A 52087-2025 artfynd.xlsx
+++ b/artfynd/A 52087-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129614106</v>
       </c>
       <c r="B2" t="n">
-        <v>97038</v>
+        <v>97050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129671481</v>
       </c>
       <c r="B3" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>129671490</v>
       </c>
       <c r="B4" t="n">
-        <v>97038</v>
+        <v>97050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129671471</v>
       </c>
       <c r="B5" t="n">
-        <v>97377</v>
+        <v>97389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129671469</v>
       </c>
       <c r="B6" t="n">
-        <v>97377</v>
+        <v>97389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129671472</v>
       </c>
       <c r="B7" t="n">
-        <v>97377</v>
+        <v>97389</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129671457</v>
       </c>
       <c r="B8" t="n">
-        <v>95992</v>
+        <v>96004</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>129671475</v>
       </c>
       <c r="B9" t="n">
-        <v>97377</v>
+        <v>97389</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>129671473</v>
       </c>
       <c r="B10" t="n">
-        <v>97377</v>
+        <v>97389</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>129671460</v>
       </c>
       <c r="B11" t="n">
-        <v>95992</v>
+        <v>96004</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>129671470</v>
       </c>
       <c r="B12" t="n">
-        <v>97377</v>
+        <v>97389</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>129671454</v>
       </c>
       <c r="B13" t="n">
-        <v>95992</v>
+        <v>96004</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>129671488</v>
       </c>
       <c r="B14" t="n">
-        <v>97038</v>
+        <v>97050</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>129671455</v>
       </c>
       <c r="B15" t="n">
-        <v>95992</v>
+        <v>96004</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>129671467</v>
       </c>
       <c r="B16" t="n">
-        <v>97377</v>
+        <v>97389</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>129671458</v>
       </c>
       <c r="B17" t="n">
-        <v>95992</v>
+        <v>96004</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>129671489</v>
       </c>
       <c r="B18" t="n">
-        <v>97038</v>
+        <v>97050</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>129671468</v>
       </c>
       <c r="B19" t="n">
-        <v>97377</v>
+        <v>97389</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>129671476</v>
       </c>
       <c r="B20" t="n">
-        <v>97377</v>
+        <v>97389</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>129671477</v>
       </c>
       <c r="B21" t="n">
-        <v>97377</v>
+        <v>97389</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>129671456</v>
       </c>
       <c r="B22" t="n">
-        <v>95992</v>
+        <v>96004</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>129671501</v>
       </c>
       <c r="B23" t="n">
-        <v>96352</v>
+        <v>96364</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>129671459</v>
       </c>
       <c r="B24" t="n">
-        <v>95992</v>
+        <v>96004</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>129671487</v>
       </c>
       <c r="B25" t="n">
-        <v>97038</v>
+        <v>97050</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>129671474</v>
       </c>
       <c r="B26" t="n">
-        <v>97377</v>
+        <v>97389</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3117,6 +3117,248 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129745963</v>
+      </c>
+      <c r="B27" t="n">
+        <v>56709</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100045</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Sångsvan</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Cygnus cygnus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gesebol 2:2, Vg</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>362701</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6401152</v>
+      </c>
+      <c r="S27" t="n">
+        <v>50</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Bo Hultgren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Bo Hultgren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129745850</v>
+      </c>
+      <c r="B28" t="n">
+        <v>56925</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gesebol 2:2, Vg</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>362701</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6401152</v>
+      </c>
+      <c r="S28" t="n">
+        <v>50</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Bo Hultgren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Bo Hultgren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52087-2025 artfynd.xlsx
+++ b/artfynd/A 52087-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129614106</v>
       </c>
       <c r="B2" t="n">
-        <v>97050</v>
+        <v>97051</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129671481</v>
       </c>
       <c r="B3" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>129671490</v>
       </c>
       <c r="B4" t="n">
-        <v>97050</v>
+        <v>97051</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129671471</v>
       </c>
       <c r="B5" t="n">
-        <v>97389</v>
+        <v>97390</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129671469</v>
       </c>
       <c r="B6" t="n">
-        <v>97389</v>
+        <v>97390</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129671472</v>
       </c>
       <c r="B7" t="n">
-        <v>97389</v>
+        <v>97390</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129671457</v>
+        <v>129671475</v>
       </c>
       <c r="B8" t="n">
-        <v>96004</v>
+        <v>97390</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>362754</v>
+        <v>362517</v>
       </c>
       <c r="R8" t="n">
-        <v>6401209</v>
+        <v>6401013</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129671475</v>
+        <v>129671457</v>
       </c>
       <c r="B9" t="n">
-        <v>97389</v>
+        <v>96005</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>362517</v>
+        <v>362754</v>
       </c>
       <c r="R9" t="n">
-        <v>6401013</v>
+        <v>6401209</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1474,7 +1474,7 @@
         <v>129671473</v>
       </c>
       <c r="B10" t="n">
-        <v>97389</v>
+        <v>97390</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>129671460</v>
       </c>
       <c r="B11" t="n">
-        <v>96004</v>
+        <v>96005</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>129671470</v>
       </c>
       <c r="B12" t="n">
-        <v>97389</v>
+        <v>97390</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1762,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129671454</v>
+        <v>129671488</v>
       </c>
       <c r="B13" t="n">
-        <v>96004</v>
+        <v>97051</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1773,21 +1773,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>362976</v>
+        <v>362944</v>
       </c>
       <c r="R13" t="n">
-        <v>6401459</v>
+        <v>6401327</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129671488</v>
+        <v>129671454</v>
       </c>
       <c r="B14" t="n">
-        <v>97050</v>
+        <v>96005</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>362944</v>
+        <v>362976</v>
       </c>
       <c r="R14" t="n">
-        <v>6401327</v>
+        <v>6401459</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1959,7 +1959,7 @@
         <v>129671455</v>
       </c>
       <c r="B15" t="n">
-        <v>96004</v>
+        <v>96005</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>129671467</v>
       </c>
       <c r="B16" t="n">
-        <v>97389</v>
+        <v>97390</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2150,10 +2150,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129671458</v>
+        <v>129671489</v>
       </c>
       <c r="B17" t="n">
-        <v>96004</v>
+        <v>97051</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2161,21 +2161,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>362492</v>
+        <v>362800</v>
       </c>
       <c r="R17" t="n">
-        <v>6400983</v>
+        <v>6401187</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129671489</v>
+        <v>129671458</v>
       </c>
       <c r="B18" t="n">
-        <v>97050</v>
+        <v>96005</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>362800</v>
+        <v>362492</v>
       </c>
       <c r="R18" t="n">
-        <v>6401187</v>
+        <v>6400983</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2347,7 +2347,7 @@
         <v>129671468</v>
       </c>
       <c r="B19" t="n">
-        <v>97389</v>
+        <v>97390</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>129671476</v>
       </c>
       <c r="B20" t="n">
-        <v>97389</v>
+        <v>97390</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>129671477</v>
       </c>
       <c r="B21" t="n">
-        <v>97389</v>
+        <v>97390</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>129671456</v>
       </c>
       <c r="B22" t="n">
-        <v>96004</v>
+        <v>96005</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>129671501</v>
       </c>
       <c r="B23" t="n">
-        <v>96364</v>
+        <v>96365</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129671459</v>
+        <v>129671487</v>
       </c>
       <c r="B24" t="n">
-        <v>96004</v>
+        <v>97051</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>362578</v>
+        <v>362989</v>
       </c>
       <c r="R24" t="n">
-        <v>6401071</v>
+        <v>6401348</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129671487</v>
+        <v>129671459</v>
       </c>
       <c r="B25" t="n">
-        <v>97050</v>
+        <v>96005</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2937,21 +2937,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>362989</v>
+        <v>362578</v>
       </c>
       <c r="R25" t="n">
-        <v>6401348</v>
+        <v>6401071</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3026,7 +3026,7 @@
         <v>129671474</v>
       </c>
       <c r="B26" t="n">
-        <v>97389</v>
+        <v>97390</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>129745963</v>
       </c>
       <c r="B27" t="n">
-        <v>56709</v>
+        <v>56710</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>129745850</v>
       </c>
       <c r="B28" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 52087-2025 artfynd.xlsx
+++ b/artfynd/A 52087-2025 artfynd.xlsx
@@ -1277,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129671475</v>
+        <v>129671457</v>
       </c>
       <c r="B8" t="n">
-        <v>97390</v>
+        <v>96005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>362517</v>
+        <v>362754</v>
       </c>
       <c r="R8" t="n">
-        <v>6401013</v>
+        <v>6401209</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129671457</v>
+        <v>129671475</v>
       </c>
       <c r="B9" t="n">
-        <v>96005</v>
+        <v>97390</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>362754</v>
+        <v>362517</v>
       </c>
       <c r="R9" t="n">
-        <v>6401209</v>
+        <v>6401013</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1762,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129671488</v>
+        <v>129671454</v>
       </c>
       <c r="B13" t="n">
-        <v>97051</v>
+        <v>96005</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1773,21 +1773,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>362944</v>
+        <v>362976</v>
       </c>
       <c r="R13" t="n">
-        <v>6401327</v>
+        <v>6401459</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1859,7 +1859,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129671454</v>
+        <v>129671455</v>
       </c>
       <c r="B14" t="n">
         <v>96005</v>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>362976</v>
+        <v>362956</v>
       </c>
       <c r="R14" t="n">
-        <v>6401459</v>
+        <v>6401313</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129671455</v>
+        <v>129671488</v>
       </c>
       <c r="B15" t="n">
-        <v>96005</v>
+        <v>97051</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>362956</v>
+        <v>362944</v>
       </c>
       <c r="R15" t="n">
-        <v>6401313</v>
+        <v>6401327</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 52087-2025 artfynd.xlsx
+++ b/artfynd/A 52087-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129614106</v>
       </c>
       <c r="B2" t="n">
-        <v>97051</v>
+        <v>97056</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129671481</v>
       </c>
       <c r="B3" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>129671490</v>
       </c>
       <c r="B4" t="n">
-        <v>97051</v>
+        <v>97056</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129671471</v>
       </c>
       <c r="B5" t="n">
-        <v>97390</v>
+        <v>97395</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129671469</v>
       </c>
       <c r="B6" t="n">
-        <v>97390</v>
+        <v>97395</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129671472</v>
       </c>
       <c r="B7" t="n">
-        <v>97390</v>
+        <v>97395</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129671457</v>
       </c>
       <c r="B8" t="n">
-        <v>96005</v>
+        <v>96010</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>129671475</v>
       </c>
       <c r="B9" t="n">
-        <v>97390</v>
+        <v>97395</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129671473</v>
+        <v>129671460</v>
       </c>
       <c r="B10" t="n">
-        <v>97390</v>
+        <v>96010</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>362642</v>
+        <v>362627</v>
       </c>
       <c r="R10" t="n">
-        <v>6401087</v>
+        <v>6401086</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129671460</v>
+        <v>129671473</v>
       </c>
       <c r="B11" t="n">
-        <v>96005</v>
+        <v>97395</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,21 +1579,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>362627</v>
+        <v>362642</v>
       </c>
       <c r="R11" t="n">
-        <v>6401086</v>
+        <v>6401087</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1668,7 +1668,7 @@
         <v>129671470</v>
       </c>
       <c r="B12" t="n">
-        <v>97390</v>
+        <v>97395</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>129671454</v>
       </c>
       <c r="B13" t="n">
-        <v>96005</v>
+        <v>96010</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129671455</v>
+        <v>129671488</v>
       </c>
       <c r="B14" t="n">
-        <v>96005</v>
+        <v>97056</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>362956</v>
+        <v>362944</v>
       </c>
       <c r="R14" t="n">
-        <v>6401313</v>
+        <v>6401327</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129671488</v>
+        <v>129671455</v>
       </c>
       <c r="B15" t="n">
-        <v>97051</v>
+        <v>96010</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>362944</v>
+        <v>362956</v>
       </c>
       <c r="R15" t="n">
-        <v>6401327</v>
+        <v>6401313</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2056,7 +2056,7 @@
         <v>129671467</v>
       </c>
       <c r="B16" t="n">
-        <v>97390</v>
+        <v>97395</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2150,10 +2150,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129671489</v>
+        <v>129671458</v>
       </c>
       <c r="B17" t="n">
-        <v>97051</v>
+        <v>96010</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2161,21 +2161,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>362800</v>
+        <v>362492</v>
       </c>
       <c r="R17" t="n">
-        <v>6401187</v>
+        <v>6400983</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129671458</v>
+        <v>129671489</v>
       </c>
       <c r="B18" t="n">
-        <v>96005</v>
+        <v>97056</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>362492</v>
+        <v>362800</v>
       </c>
       <c r="R18" t="n">
-        <v>6400983</v>
+        <v>6401187</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2347,7 +2347,7 @@
         <v>129671468</v>
       </c>
       <c r="B19" t="n">
-        <v>97390</v>
+        <v>97395</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>129671476</v>
       </c>
       <c r="B20" t="n">
-        <v>97390</v>
+        <v>97395</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>129671477</v>
       </c>
       <c r="B21" t="n">
-        <v>97390</v>
+        <v>97395</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>129671456</v>
       </c>
       <c r="B22" t="n">
-        <v>96005</v>
+        <v>96010</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>129671501</v>
       </c>
       <c r="B23" t="n">
-        <v>96365</v>
+        <v>96370</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129671487</v>
+        <v>129671459</v>
       </c>
       <c r="B24" t="n">
-        <v>97051</v>
+        <v>96010</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>362989</v>
+        <v>362578</v>
       </c>
       <c r="R24" t="n">
-        <v>6401348</v>
+        <v>6401071</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129671459</v>
+        <v>129671487</v>
       </c>
       <c r="B25" t="n">
-        <v>96005</v>
+        <v>97056</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2937,21 +2937,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>362578</v>
+        <v>362989</v>
       </c>
       <c r="R25" t="n">
-        <v>6401071</v>
+        <v>6401348</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3026,7 +3026,7 @@
         <v>129671474</v>
       </c>
       <c r="B26" t="n">
-        <v>97390</v>
+        <v>97395</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 52087-2025 artfynd.xlsx
+++ b/artfynd/A 52087-2025 artfynd.xlsx
@@ -1471,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129671460</v>
+        <v>129671473</v>
       </c>
       <c r="B10" t="n">
-        <v>96010</v>
+        <v>97395</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>362627</v>
+        <v>362642</v>
       </c>
       <c r="R10" t="n">
-        <v>6401086</v>
+        <v>6401087</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129671473</v>
+        <v>129671460</v>
       </c>
       <c r="B11" t="n">
-        <v>97395</v>
+        <v>96010</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,21 +1579,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>362642</v>
+        <v>362627</v>
       </c>
       <c r="R11" t="n">
-        <v>6401087</v>
+        <v>6401086</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 52087-2025 artfynd.xlsx
+++ b/artfynd/A 52087-2025 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129671469</v>
+        <v>129671457</v>
       </c>
       <c r="B6" t="n">
-        <v>97395</v>
+        <v>96010</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>362839</v>
+        <v>362754</v>
       </c>
       <c r="R6" t="n">
-        <v>6401219</v>
+        <v>6401209</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129671472</v>
+        <v>129671469</v>
       </c>
       <c r="B7" t="n">
         <v>97395</v>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>362650</v>
+        <v>362839</v>
       </c>
       <c r="R7" t="n">
-        <v>6401137</v>
+        <v>6401219</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129671457</v>
+        <v>129671472</v>
       </c>
       <c r="B8" t="n">
-        <v>96010</v>
+        <v>97395</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>362754</v>
+        <v>362650</v>
       </c>
       <c r="R8" t="n">
-        <v>6401209</v>
+        <v>6401137</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129671473</v>
+        <v>129671460</v>
       </c>
       <c r="B10" t="n">
-        <v>97395</v>
+        <v>96010</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>362642</v>
+        <v>362627</v>
       </c>
       <c r="R10" t="n">
-        <v>6401087</v>
+        <v>6401086</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129671460</v>
+        <v>129671473</v>
       </c>
       <c r="B11" t="n">
-        <v>96010</v>
+        <v>97395</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,21 +1579,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>362627</v>
+        <v>362642</v>
       </c>
       <c r="R11" t="n">
-        <v>6401086</v>
+        <v>6401087</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1762,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129671454</v>
+        <v>129671488</v>
       </c>
       <c r="B13" t="n">
-        <v>96010</v>
+        <v>97056</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1773,21 +1773,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>362976</v>
+        <v>362944</v>
       </c>
       <c r="R13" t="n">
-        <v>6401459</v>
+        <v>6401327</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129671488</v>
+        <v>129671454</v>
       </c>
       <c r="B14" t="n">
-        <v>97056</v>
+        <v>96010</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>362944</v>
+        <v>362976</v>
       </c>
       <c r="R14" t="n">
-        <v>6401327</v>
+        <v>6401459</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2150,10 +2150,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129671458</v>
+        <v>129671489</v>
       </c>
       <c r="B17" t="n">
-        <v>96010</v>
+        <v>97056</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2161,21 +2161,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>362492</v>
+        <v>362800</v>
       </c>
       <c r="R17" t="n">
-        <v>6400983</v>
+        <v>6401187</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129671489</v>
+        <v>129671458</v>
       </c>
       <c r="B18" t="n">
-        <v>97056</v>
+        <v>96010</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>362800</v>
+        <v>362492</v>
       </c>
       <c r="R18" t="n">
-        <v>6401187</v>
+        <v>6400983</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>

--- a/artfynd/A 52087-2025 artfynd.xlsx
+++ b/artfynd/A 52087-2025 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129671457</v>
+        <v>129671469</v>
       </c>
       <c r="B6" t="n">
-        <v>96010</v>
+        <v>97395</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>362754</v>
+        <v>362839</v>
       </c>
       <c r="R6" t="n">
-        <v>6401209</v>
+        <v>6401219</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129671469</v>
+        <v>129671472</v>
       </c>
       <c r="B7" t="n">
         <v>97395</v>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>362839</v>
+        <v>362650</v>
       </c>
       <c r="R7" t="n">
-        <v>6401219</v>
+        <v>6401137</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1277,7 +1277,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129671472</v>
+        <v>129671475</v>
       </c>
       <c r="B8" t="n">
         <v>97395</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>362650</v>
+        <v>362517</v>
       </c>
       <c r="R8" t="n">
-        <v>6401137</v>
+        <v>6401013</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129671475</v>
+        <v>129671457</v>
       </c>
       <c r="B9" t="n">
-        <v>97395</v>
+        <v>96010</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>362517</v>
+        <v>362754</v>
       </c>
       <c r="R9" t="n">
-        <v>6401013</v>
+        <v>6401209</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129671460</v>
+        <v>129671473</v>
       </c>
       <c r="B10" t="n">
-        <v>96010</v>
+        <v>97395</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>362627</v>
+        <v>362642</v>
       </c>
       <c r="R10" t="n">
-        <v>6401086</v>
+        <v>6401087</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129671473</v>
+        <v>129671460</v>
       </c>
       <c r="B11" t="n">
-        <v>97395</v>
+        <v>96010</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,21 +1579,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>362642</v>
+        <v>362627</v>
       </c>
       <c r="R11" t="n">
-        <v>6401087</v>
+        <v>6401086</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -2635,10 +2635,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129671456</v>
+        <v>129671501</v>
       </c>
       <c r="B22" t="n">
-        <v>96010</v>
+        <v>96370</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2646,21 +2646,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>362809</v>
+        <v>362633</v>
       </c>
       <c r="R22" t="n">
-        <v>6401252</v>
+        <v>6401090</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129671501</v>
+        <v>129671456</v>
       </c>
       <c r="B23" t="n">
-        <v>96370</v>
+        <v>96010</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2743,21 +2743,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>362633</v>
+        <v>362809</v>
       </c>
       <c r="R23" t="n">
-        <v>6401090</v>
+        <v>6401252</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129671459</v>
+        <v>129671487</v>
       </c>
       <c r="B24" t="n">
-        <v>96010</v>
+        <v>97056</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>362578</v>
+        <v>362989</v>
       </c>
       <c r="R24" t="n">
-        <v>6401071</v>
+        <v>6401348</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129671487</v>
+        <v>129671459</v>
       </c>
       <c r="B25" t="n">
-        <v>97056</v>
+        <v>96010</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2937,21 +2937,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>362989</v>
+        <v>362578</v>
       </c>
       <c r="R25" t="n">
-        <v>6401348</v>
+        <v>6401071</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>

--- a/artfynd/A 52087-2025 artfynd.xlsx
+++ b/artfynd/A 52087-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129614106</v>
       </c>
       <c r="B2" t="n">
-        <v>97056</v>
+        <v>97060</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129671481</v>
       </c>
       <c r="B3" t="n">
-        <v>97645</v>
+        <v>97649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>129671490</v>
       </c>
       <c r="B4" t="n">
-        <v>97056</v>
+        <v>97060</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129671471</v>
       </c>
       <c r="B5" t="n">
-        <v>97395</v>
+        <v>97399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129671469</v>
       </c>
       <c r="B6" t="n">
-        <v>97395</v>
+        <v>97399</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129671472</v>
       </c>
       <c r="B7" t="n">
-        <v>97395</v>
+        <v>97399</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129671475</v>
       </c>
       <c r="B8" t="n">
-        <v>97395</v>
+        <v>97399</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>129671457</v>
       </c>
       <c r="B9" t="n">
-        <v>96010</v>
+        <v>96014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129671473</v>
+        <v>129671460</v>
       </c>
       <c r="B10" t="n">
-        <v>97395</v>
+        <v>96014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>362642</v>
+        <v>362627</v>
       </c>
       <c r="R10" t="n">
-        <v>6401087</v>
+        <v>6401086</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129671460</v>
+        <v>129671473</v>
       </c>
       <c r="B11" t="n">
-        <v>96010</v>
+        <v>97399</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,21 +1579,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>362627</v>
+        <v>362642</v>
       </c>
       <c r="R11" t="n">
-        <v>6401086</v>
+        <v>6401087</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1668,7 +1668,7 @@
         <v>129671470</v>
       </c>
       <c r="B12" t="n">
-        <v>97395</v>
+        <v>97399</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1762,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129671488</v>
+        <v>129671454</v>
       </c>
       <c r="B13" t="n">
-        <v>97056</v>
+        <v>96014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1773,21 +1773,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>362944</v>
+        <v>362976</v>
       </c>
       <c r="R13" t="n">
-        <v>6401327</v>
+        <v>6401459</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129671454</v>
+        <v>129671455</v>
       </c>
       <c r="B14" t="n">
-        <v>96010</v>
+        <v>96014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>362976</v>
+        <v>362956</v>
       </c>
       <c r="R14" t="n">
-        <v>6401459</v>
+        <v>6401313</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129671455</v>
+        <v>129671488</v>
       </c>
       <c r="B15" t="n">
-        <v>96010</v>
+        <v>97060</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>362956</v>
+        <v>362944</v>
       </c>
       <c r="R15" t="n">
-        <v>6401313</v>
+        <v>6401327</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2056,7 +2056,7 @@
         <v>129671467</v>
       </c>
       <c r="B16" t="n">
-        <v>97395</v>
+        <v>97399</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2150,10 +2150,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129671489</v>
+        <v>129671458</v>
       </c>
       <c r="B17" t="n">
-        <v>97056</v>
+        <v>96014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2161,21 +2161,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>362800</v>
+        <v>362492</v>
       </c>
       <c r="R17" t="n">
-        <v>6401187</v>
+        <v>6400983</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129671458</v>
+        <v>129671489</v>
       </c>
       <c r="B18" t="n">
-        <v>96010</v>
+        <v>97060</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>362492</v>
+        <v>362800</v>
       </c>
       <c r="R18" t="n">
-        <v>6400983</v>
+        <v>6401187</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2347,7 +2347,7 @@
         <v>129671468</v>
       </c>
       <c r="B19" t="n">
-        <v>97395</v>
+        <v>97399</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>129671476</v>
       </c>
       <c r="B20" t="n">
-        <v>97395</v>
+        <v>97399</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>129671477</v>
       </c>
       <c r="B21" t="n">
-        <v>97395</v>
+        <v>97399</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>129671501</v>
       </c>
       <c r="B22" t="n">
-        <v>96370</v>
+        <v>96374</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>129671456</v>
       </c>
       <c r="B23" t="n">
-        <v>96010</v>
+        <v>96014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>129671487</v>
       </c>
       <c r="B24" t="n">
-        <v>97056</v>
+        <v>97060</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>129671459</v>
       </c>
       <c r="B25" t="n">
-        <v>96010</v>
+        <v>96014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>129671474</v>
       </c>
       <c r="B26" t="n">
-        <v>97395</v>
+        <v>97399</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 52087-2025 artfynd.xlsx
+++ b/artfynd/A 52087-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129614106</v>
       </c>
       <c r="B2" t="n">
-        <v>97060</v>
+        <v>97062</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129671481</v>
       </c>
       <c r="B3" t="n">
-        <v>97649</v>
+        <v>97651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>129671490</v>
       </c>
       <c r="B4" t="n">
-        <v>97060</v>
+        <v>97062</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129671471</v>
       </c>
       <c r="B5" t="n">
-        <v>97399</v>
+        <v>97401</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129671469</v>
       </c>
       <c r="B6" t="n">
-        <v>97399</v>
+        <v>97401</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129671472</v>
       </c>
       <c r="B7" t="n">
-        <v>97399</v>
+        <v>97401</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129671475</v>
       </c>
       <c r="B8" t="n">
-        <v>97399</v>
+        <v>97401</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>129671457</v>
       </c>
       <c r="B9" t="n">
-        <v>96014</v>
+        <v>96016</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129671460</v>
+        <v>129671473</v>
       </c>
       <c r="B10" t="n">
-        <v>96014</v>
+        <v>97401</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>362627</v>
+        <v>362642</v>
       </c>
       <c r="R10" t="n">
-        <v>6401086</v>
+        <v>6401087</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129671473</v>
+        <v>129671460</v>
       </c>
       <c r="B11" t="n">
-        <v>97399</v>
+        <v>96016</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,21 +1579,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>362642</v>
+        <v>362627</v>
       </c>
       <c r="R11" t="n">
-        <v>6401087</v>
+        <v>6401086</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1668,7 +1668,7 @@
         <v>129671470</v>
       </c>
       <c r="B12" t="n">
-        <v>97399</v>
+        <v>97401</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1762,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129671454</v>
+        <v>129671455</v>
       </c>
       <c r="B13" t="n">
-        <v>96014</v>
+        <v>96016</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>362976</v>
+        <v>362956</v>
       </c>
       <c r="R13" t="n">
-        <v>6401459</v>
+        <v>6401313</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129671455</v>
+        <v>129671488</v>
       </c>
       <c r="B14" t="n">
-        <v>96014</v>
+        <v>97062</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>362956</v>
+        <v>362944</v>
       </c>
       <c r="R14" t="n">
-        <v>6401313</v>
+        <v>6401327</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129671488</v>
+        <v>129671454</v>
       </c>
       <c r="B15" t="n">
-        <v>97060</v>
+        <v>96016</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>362944</v>
+        <v>362976</v>
       </c>
       <c r="R15" t="n">
-        <v>6401327</v>
+        <v>6401459</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2056,7 +2056,7 @@
         <v>129671467</v>
       </c>
       <c r="B16" t="n">
-        <v>97399</v>
+        <v>97401</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2150,10 +2150,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129671458</v>
+        <v>129671489</v>
       </c>
       <c r="B17" t="n">
-        <v>96014</v>
+        <v>97062</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2161,21 +2161,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>362492</v>
+        <v>362800</v>
       </c>
       <c r="R17" t="n">
-        <v>6400983</v>
+        <v>6401187</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129671489</v>
+        <v>129671458</v>
       </c>
       <c r="B18" t="n">
-        <v>97060</v>
+        <v>96016</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>362800</v>
+        <v>362492</v>
       </c>
       <c r="R18" t="n">
-        <v>6401187</v>
+        <v>6400983</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2347,7 +2347,7 @@
         <v>129671468</v>
       </c>
       <c r="B19" t="n">
-        <v>97399</v>
+        <v>97401</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>129671476</v>
       </c>
       <c r="B20" t="n">
-        <v>97399</v>
+        <v>97401</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>129671477</v>
       </c>
       <c r="B21" t="n">
-        <v>97399</v>
+        <v>97401</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>129671501</v>
       </c>
       <c r="B22" t="n">
-        <v>96374</v>
+        <v>96376</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>129671456</v>
       </c>
       <c r="B23" t="n">
-        <v>96014</v>
+        <v>96016</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>129671487</v>
       </c>
       <c r="B24" t="n">
-        <v>97060</v>
+        <v>97062</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>129671459</v>
       </c>
       <c r="B25" t="n">
-        <v>96014</v>
+        <v>96016</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>129671474</v>
       </c>
       <c r="B26" t="n">
-        <v>97399</v>
+        <v>97401</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 52087-2025 artfynd.xlsx
+++ b/artfynd/A 52087-2025 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129671469</v>
+        <v>129671457</v>
       </c>
       <c r="B6" t="n">
-        <v>97401</v>
+        <v>96016</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>362839</v>
+        <v>362754</v>
       </c>
       <c r="R6" t="n">
-        <v>6401219</v>
+        <v>6401209</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129671472</v>
+        <v>129671469</v>
       </c>
       <c r="B7" t="n">
         <v>97401</v>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>362650</v>
+        <v>362839</v>
       </c>
       <c r="R7" t="n">
-        <v>6401137</v>
+        <v>6401219</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1277,7 +1277,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129671475</v>
+        <v>129671472</v>
       </c>
       <c r="B8" t="n">
         <v>97401</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>362517</v>
+        <v>362650</v>
       </c>
       <c r="R8" t="n">
-        <v>6401013</v>
+        <v>6401137</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129671457</v>
+        <v>129671475</v>
       </c>
       <c r="B9" t="n">
-        <v>96016</v>
+        <v>97401</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>362754</v>
+        <v>362517</v>
       </c>
       <c r="R9" t="n">
-        <v>6401209</v>
+        <v>6401013</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 52087-2025 artfynd.xlsx
+++ b/artfynd/A 52087-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129614106</v>
       </c>
       <c r="B2" t="n">
-        <v>97062</v>
+        <v>97072</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129671481</v>
       </c>
       <c r="B3" t="n">
-        <v>97651</v>
+        <v>97661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>129671490</v>
       </c>
       <c r="B4" t="n">
-        <v>97062</v>
+        <v>97072</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129671471</v>
       </c>
       <c r="B5" t="n">
-        <v>97401</v>
+        <v>97411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129671457</v>
+        <v>129671469</v>
       </c>
       <c r="B6" t="n">
-        <v>96016</v>
+        <v>97411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>362754</v>
+        <v>362839</v>
       </c>
       <c r="R6" t="n">
-        <v>6401209</v>
+        <v>6401219</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129671469</v>
+        <v>129671472</v>
       </c>
       <c r="B7" t="n">
-        <v>97401</v>
+        <v>97411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>362839</v>
+        <v>362650</v>
       </c>
       <c r="R7" t="n">
-        <v>6401219</v>
+        <v>6401137</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129671472</v>
+        <v>129671475</v>
       </c>
       <c r="B8" t="n">
-        <v>97401</v>
+        <v>97411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>362650</v>
+        <v>362517</v>
       </c>
       <c r="R8" t="n">
-        <v>6401137</v>
+        <v>6401013</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129671475</v>
+        <v>129671457</v>
       </c>
       <c r="B9" t="n">
-        <v>97401</v>
+        <v>96026</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>362517</v>
+        <v>362754</v>
       </c>
       <c r="R9" t="n">
-        <v>6401013</v>
+        <v>6401209</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1474,7 +1474,7 @@
         <v>129671473</v>
       </c>
       <c r="B10" t="n">
-        <v>97401</v>
+        <v>97411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>129671460</v>
       </c>
       <c r="B11" t="n">
-        <v>96016</v>
+        <v>96026</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>129671470</v>
       </c>
       <c r="B12" t="n">
-        <v>97401</v>
+        <v>97411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1762,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129671455</v>
+        <v>129671454</v>
       </c>
       <c r="B13" t="n">
-        <v>96016</v>
+        <v>96026</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>362956</v>
+        <v>362976</v>
       </c>
       <c r="R13" t="n">
-        <v>6401313</v>
+        <v>6401459</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129671488</v>
+        <v>129671455</v>
       </c>
       <c r="B14" t="n">
-        <v>97062</v>
+        <v>96026</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>362944</v>
+        <v>362956</v>
       </c>
       <c r="R14" t="n">
-        <v>6401327</v>
+        <v>6401313</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129671454</v>
+        <v>129671488</v>
       </c>
       <c r="B15" t="n">
-        <v>96016</v>
+        <v>97072</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>362976</v>
+        <v>362944</v>
       </c>
       <c r="R15" t="n">
-        <v>6401459</v>
+        <v>6401327</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2056,7 +2056,7 @@
         <v>129671467</v>
       </c>
       <c r="B16" t="n">
-        <v>97401</v>
+        <v>97411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>129671489</v>
       </c>
       <c r="B17" t="n">
-        <v>97062</v>
+        <v>97072</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>129671458</v>
       </c>
       <c r="B18" t="n">
-        <v>96016</v>
+        <v>96026</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>129671468</v>
       </c>
       <c r="B19" t="n">
-        <v>97401</v>
+        <v>97411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>129671476</v>
       </c>
       <c r="B20" t="n">
-        <v>97401</v>
+        <v>97411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>129671477</v>
       </c>
       <c r="B21" t="n">
-        <v>97401</v>
+        <v>97411</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>129671501</v>
       </c>
       <c r="B22" t="n">
-        <v>96376</v>
+        <v>96386</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>129671456</v>
       </c>
       <c r="B23" t="n">
-        <v>96016</v>
+        <v>96026</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>129671487</v>
       </c>
       <c r="B24" t="n">
-        <v>97062</v>
+        <v>97072</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>129671459</v>
       </c>
       <c r="B25" t="n">
-        <v>96016</v>
+        <v>96026</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>129671474</v>
       </c>
       <c r="B26" t="n">
-        <v>97401</v>
+        <v>97411</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 52087-2025 artfynd.xlsx
+++ b/artfynd/A 52087-2025 artfynd.xlsx
@@ -1471,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129671473</v>
+        <v>129671460</v>
       </c>
       <c r="B10" t="n">
-        <v>97411</v>
+        <v>96026</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>362642</v>
+        <v>362627</v>
       </c>
       <c r="R10" t="n">
-        <v>6401087</v>
+        <v>6401086</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129671460</v>
+        <v>129671473</v>
       </c>
       <c r="B11" t="n">
-        <v>96026</v>
+        <v>97411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,21 +1579,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>362627</v>
+        <v>362642</v>
       </c>
       <c r="R11" t="n">
-        <v>6401086</v>
+        <v>6401087</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -3242,7 +3242,7 @@
         <v>129745850</v>
       </c>
       <c r="B28" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 52087-2025 artfynd.xlsx
+++ b/artfynd/A 52087-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129614106</v>
       </c>
       <c r="B2" t="n">
-        <v>97072</v>
+        <v>97076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129671481</v>
       </c>
       <c r="B3" t="n">
-        <v>97661</v>
+        <v>97665</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>129671490</v>
       </c>
       <c r="B4" t="n">
-        <v>97072</v>
+        <v>97076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129671471</v>
       </c>
       <c r="B5" t="n">
-        <v>97411</v>
+        <v>97415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129671469</v>
       </c>
       <c r="B6" t="n">
-        <v>97411</v>
+        <v>97415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129671472</v>
       </c>
       <c r="B7" t="n">
-        <v>97411</v>
+        <v>97415</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129671475</v>
+        <v>129671457</v>
       </c>
       <c r="B8" t="n">
-        <v>97411</v>
+        <v>96030</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>362517</v>
+        <v>362754</v>
       </c>
       <c r="R8" t="n">
-        <v>6401013</v>
+        <v>6401209</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129671457</v>
+        <v>129671475</v>
       </c>
       <c r="B9" t="n">
-        <v>96026</v>
+        <v>97415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>362754</v>
+        <v>362517</v>
       </c>
       <c r="R9" t="n">
-        <v>6401209</v>
+        <v>6401013</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129671460</v>
+        <v>129671473</v>
       </c>
       <c r="B10" t="n">
-        <v>96026</v>
+        <v>97415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>362627</v>
+        <v>362642</v>
       </c>
       <c r="R10" t="n">
-        <v>6401086</v>
+        <v>6401087</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129671473</v>
+        <v>129671460</v>
       </c>
       <c r="B11" t="n">
-        <v>97411</v>
+        <v>96030</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,21 +1579,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>362642</v>
+        <v>362627</v>
       </c>
       <c r="R11" t="n">
-        <v>6401087</v>
+        <v>6401086</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1668,7 +1668,7 @@
         <v>129671470</v>
       </c>
       <c r="B12" t="n">
-        <v>97411</v>
+        <v>97415</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>129671454</v>
       </c>
       <c r="B13" t="n">
-        <v>96026</v>
+        <v>96030</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129671455</v>
+        <v>129671488</v>
       </c>
       <c r="B14" t="n">
-        <v>96026</v>
+        <v>97076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>362956</v>
+        <v>362944</v>
       </c>
       <c r="R14" t="n">
-        <v>6401313</v>
+        <v>6401327</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129671488</v>
+        <v>129671455</v>
       </c>
       <c r="B15" t="n">
-        <v>97072</v>
+        <v>96030</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>362944</v>
+        <v>362956</v>
       </c>
       <c r="R15" t="n">
-        <v>6401327</v>
+        <v>6401313</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2056,7 +2056,7 @@
         <v>129671467</v>
       </c>
       <c r="B16" t="n">
-        <v>97411</v>
+        <v>97415</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2150,10 +2150,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129671489</v>
+        <v>129671458</v>
       </c>
       <c r="B17" t="n">
-        <v>97072</v>
+        <v>96030</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2161,21 +2161,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>362800</v>
+        <v>362492</v>
       </c>
       <c r="R17" t="n">
-        <v>6401187</v>
+        <v>6400983</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129671458</v>
+        <v>129671489</v>
       </c>
       <c r="B18" t="n">
-        <v>96026</v>
+        <v>97076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>362492</v>
+        <v>362800</v>
       </c>
       <c r="R18" t="n">
-        <v>6400983</v>
+        <v>6401187</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2347,7 +2347,7 @@
         <v>129671468</v>
       </c>
       <c r="B19" t="n">
-        <v>97411</v>
+        <v>97415</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>129671476</v>
       </c>
       <c r="B20" t="n">
-        <v>97411</v>
+        <v>97415</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>129671477</v>
       </c>
       <c r="B21" t="n">
-        <v>97411</v>
+        <v>97415</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2635,10 +2635,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129671501</v>
+        <v>129671456</v>
       </c>
       <c r="B22" t="n">
-        <v>96386</v>
+        <v>96030</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2646,21 +2646,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>362633</v>
+        <v>362809</v>
       </c>
       <c r="R22" t="n">
-        <v>6401090</v>
+        <v>6401252</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129671456</v>
+        <v>129671501</v>
       </c>
       <c r="B23" t="n">
-        <v>96026</v>
+        <v>96390</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2743,21 +2743,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>362809</v>
+        <v>362633</v>
       </c>
       <c r="R23" t="n">
-        <v>6401252</v>
+        <v>6401090</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129671487</v>
+        <v>129671459</v>
       </c>
       <c r="B24" t="n">
-        <v>97072</v>
+        <v>96030</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>362989</v>
+        <v>362578</v>
       </c>
       <c r="R24" t="n">
-        <v>6401348</v>
+        <v>6401071</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129671459</v>
+        <v>129671487</v>
       </c>
       <c r="B25" t="n">
-        <v>96026</v>
+        <v>97076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2937,21 +2937,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>362578</v>
+        <v>362989</v>
       </c>
       <c r="R25" t="n">
-        <v>6401071</v>
+        <v>6401348</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3026,7 +3026,7 @@
         <v>129671474</v>
       </c>
       <c r="B26" t="n">
-        <v>97411</v>
+        <v>97415</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 52087-2025 artfynd.xlsx
+++ b/artfynd/A 52087-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129614106</v>
       </c>
       <c r="B2" t="n">
-        <v>97076</v>
+        <v>97079</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129671481</v>
       </c>
       <c r="B3" t="n">
-        <v>97665</v>
+        <v>97668</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>129671490</v>
       </c>
       <c r="B4" t="n">
-        <v>97076</v>
+        <v>97079</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129671471</v>
       </c>
       <c r="B5" t="n">
-        <v>97415</v>
+        <v>97418</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129671469</v>
       </c>
       <c r="B6" t="n">
-        <v>97415</v>
+        <v>97418</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129671472</v>
       </c>
       <c r="B7" t="n">
-        <v>97415</v>
+        <v>97418</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129671457</v>
       </c>
       <c r="B8" t="n">
-        <v>96030</v>
+        <v>96033</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>129671475</v>
       </c>
       <c r="B9" t="n">
-        <v>97415</v>
+        <v>97418</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>129671473</v>
       </c>
       <c r="B10" t="n">
-        <v>97415</v>
+        <v>97418</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>129671460</v>
       </c>
       <c r="B11" t="n">
-        <v>96030</v>
+        <v>96033</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>129671470</v>
       </c>
       <c r="B12" t="n">
-        <v>97415</v>
+        <v>97418</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>129671454</v>
       </c>
       <c r="B13" t="n">
-        <v>96030</v>
+        <v>96033</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>129671488</v>
       </c>
       <c r="B14" t="n">
-        <v>97076</v>
+        <v>97079</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>129671455</v>
       </c>
       <c r="B15" t="n">
-        <v>96030</v>
+        <v>96033</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>129671467</v>
       </c>
       <c r="B16" t="n">
-        <v>97415</v>
+        <v>97418</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>129671458</v>
       </c>
       <c r="B17" t="n">
-        <v>96030</v>
+        <v>96033</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>129671489</v>
       </c>
       <c r="B18" t="n">
-        <v>97076</v>
+        <v>97079</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>129671468</v>
       </c>
       <c r="B19" t="n">
-        <v>97415</v>
+        <v>97418</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>129671476</v>
       </c>
       <c r="B20" t="n">
-        <v>97415</v>
+        <v>97418</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>129671477</v>
       </c>
       <c r="B21" t="n">
-        <v>97415</v>
+        <v>97418</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>129671456</v>
       </c>
       <c r="B22" t="n">
-        <v>96030</v>
+        <v>96033</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>129671501</v>
       </c>
       <c r="B23" t="n">
-        <v>96390</v>
+        <v>96393</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>129671459</v>
       </c>
       <c r="B24" t="n">
-        <v>96030</v>
+        <v>96033</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>129671487</v>
       </c>
       <c r="B25" t="n">
-        <v>97076</v>
+        <v>97079</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>129671474</v>
       </c>
       <c r="B26" t="n">
-        <v>97415</v>
+        <v>97418</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>129745963</v>
       </c>
       <c r="B27" t="n">
-        <v>56710</v>
+        <v>56713</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>129745850</v>
       </c>
       <c r="B28" t="n">
-        <v>56927</v>
+        <v>56930</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 52087-2025 artfynd.xlsx
+++ b/artfynd/A 52087-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129671481</v>
       </c>
       <c r="B3" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>129671490</v>
       </c>
       <c r="B4" t="n">
-        <v>97079</v>
+        <v>97080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129671471</v>
       </c>
       <c r="B5" t="n">
-        <v>97418</v>
+        <v>97419</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129671469</v>
+        <v>129671457</v>
       </c>
       <c r="B6" t="n">
-        <v>97418</v>
+        <v>96034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>362839</v>
+        <v>362754</v>
       </c>
       <c r="R6" t="n">
-        <v>6401219</v>
+        <v>6401209</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129671472</v>
+        <v>129671469</v>
       </c>
       <c r="B7" t="n">
-        <v>97418</v>
+        <v>97419</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>362650</v>
+        <v>362839</v>
       </c>
       <c r="R7" t="n">
-        <v>6401137</v>
+        <v>6401219</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129671457</v>
+        <v>129671472</v>
       </c>
       <c r="B8" t="n">
-        <v>96033</v>
+        <v>97419</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>362754</v>
+        <v>362650</v>
       </c>
       <c r="R8" t="n">
-        <v>6401209</v>
+        <v>6401137</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1377,7 +1377,7 @@
         <v>129671475</v>
       </c>
       <c r="B9" t="n">
-        <v>97418</v>
+        <v>97419</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>129671473</v>
       </c>
       <c r="B10" t="n">
-        <v>97418</v>
+        <v>97419</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>129671460</v>
       </c>
       <c r="B11" t="n">
-        <v>96033</v>
+        <v>96034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>129671470</v>
       </c>
       <c r="B12" t="n">
-        <v>97418</v>
+        <v>97419</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>129671454</v>
       </c>
       <c r="B13" t="n">
-        <v>96033</v>
+        <v>96034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>129671488</v>
       </c>
       <c r="B14" t="n">
-        <v>97079</v>
+        <v>97080</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>129671455</v>
       </c>
       <c r="B15" t="n">
-        <v>96033</v>
+        <v>96034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>129671467</v>
       </c>
       <c r="B16" t="n">
-        <v>97418</v>
+        <v>97419</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>129671458</v>
       </c>
       <c r="B17" t="n">
-        <v>96033</v>
+        <v>96034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>129671489</v>
       </c>
       <c r="B18" t="n">
-        <v>97079</v>
+        <v>97080</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>129671468</v>
       </c>
       <c r="B19" t="n">
-        <v>97418</v>
+        <v>97419</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>129671476</v>
       </c>
       <c r="B20" t="n">
-        <v>97418</v>
+        <v>97419</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>129671477</v>
       </c>
       <c r="B21" t="n">
-        <v>97418</v>
+        <v>97419</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>129671456</v>
       </c>
       <c r="B22" t="n">
-        <v>96033</v>
+        <v>96034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>129671501</v>
       </c>
       <c r="B23" t="n">
-        <v>96393</v>
+        <v>96394</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>129671459</v>
       </c>
       <c r="B24" t="n">
-        <v>96033</v>
+        <v>96034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>129671487</v>
       </c>
       <c r="B25" t="n">
-        <v>97079</v>
+        <v>97080</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>129671474</v>
       </c>
       <c r="B26" t="n">
-        <v>97418</v>
+        <v>97419</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 52087-2025 artfynd.xlsx
+++ b/artfynd/A 52087-2025 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129671457</v>
+        <v>129671469</v>
       </c>
       <c r="B6" t="n">
-        <v>96034</v>
+        <v>97419</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>362754</v>
+        <v>362839</v>
       </c>
       <c r="R6" t="n">
-        <v>6401209</v>
+        <v>6401219</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129671469</v>
+        <v>129671472</v>
       </c>
       <c r="B7" t="n">
         <v>97419</v>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>362839</v>
+        <v>362650</v>
       </c>
       <c r="R7" t="n">
-        <v>6401219</v>
+        <v>6401137</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129671472</v>
+        <v>129671457</v>
       </c>
       <c r="B8" t="n">
-        <v>97419</v>
+        <v>96034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>362650</v>
+        <v>362754</v>
       </c>
       <c r="R8" t="n">
-        <v>6401137</v>
+        <v>6401209</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -2635,10 +2635,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129671456</v>
+        <v>129671501</v>
       </c>
       <c r="B22" t="n">
-        <v>96034</v>
+        <v>96394</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2646,21 +2646,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>362809</v>
+        <v>362633</v>
       </c>
       <c r="R22" t="n">
-        <v>6401252</v>
+        <v>6401090</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129671501</v>
+        <v>129671456</v>
       </c>
       <c r="B23" t="n">
-        <v>96394</v>
+        <v>96034</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2743,21 +2743,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>362633</v>
+        <v>362809</v>
       </c>
       <c r="R23" t="n">
-        <v>6401090</v>
+        <v>6401252</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>

--- a/artfynd/A 52087-2025 artfynd.xlsx
+++ b/artfynd/A 52087-2025 artfynd.xlsx
@@ -3242,7 +3242,7 @@
         <v>129745850</v>
       </c>
       <c r="B28" t="n">
-        <v>56930</v>
+        <v>57053</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 52087-2025 artfynd.xlsx
+++ b/artfynd/A 52087-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129614106</v>
+        <v>129671501</v>
       </c>
       <c r="B2" t="n">
-        <v>97079</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,41 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2590</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mjögasjön, Vg</t>
+          <t>Gesebol, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>362800</v>
+        <v>362633</v>
       </c>
       <c r="R2" t="n">
-        <v>6401256</v>
+        <v>6401090</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:23</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>1 låga med kornknutmossa</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tobias Federsel</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tobias Federsel</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129671481</v>
+        <v>129671467</v>
       </c>
       <c r="B3" t="n">
-        <v>97669</v>
+        <v>97733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>362639</v>
+        <v>362965</v>
       </c>
       <c r="R3" t="n">
-        <v>6401070</v>
+        <v>6401425</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -888,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129671490</v>
+        <v>129671468</v>
       </c>
       <c r="B4" t="n">
-        <v>97080</v>
+        <v>97733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2590</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>362834</v>
+        <v>362966</v>
       </c>
       <c r="R4" t="n">
-        <v>6401233</v>
+        <v>6401361</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -967,7 +948,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -986,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129671471</v>
+        <v>129671469</v>
       </c>
       <c r="B5" t="n">
-        <v>97419</v>
+        <v>97733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>362808</v>
+        <v>362839</v>
       </c>
       <c r="R5" t="n">
-        <v>6401246</v>
+        <v>6401219</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1083,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129671469</v>
+        <v>129671470</v>
       </c>
       <c r="B6" t="n">
-        <v>97419</v>
+        <v>97733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>362839</v>
+        <v>362943</v>
       </c>
       <c r="R6" t="n">
-        <v>6401219</v>
+        <v>6401326</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1180,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129671472</v>
+        <v>129671471</v>
       </c>
       <c r="B7" t="n">
-        <v>97419</v>
+        <v>97733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>362650</v>
+        <v>362808</v>
       </c>
       <c r="R7" t="n">
-        <v>6401137</v>
+        <v>6401246</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1277,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129671457</v>
+        <v>129671472</v>
       </c>
       <c r="B8" t="n">
-        <v>96034</v>
+        <v>97733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>362754</v>
+        <v>362650</v>
       </c>
       <c r="R8" t="n">
-        <v>6401209</v>
+        <v>6401137</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1374,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129671475</v>
+        <v>129671473</v>
       </c>
       <c r="B9" t="n">
-        <v>97419</v>
+        <v>97733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>362517</v>
+        <v>362642</v>
       </c>
       <c r="R9" t="n">
-        <v>6401013</v>
+        <v>6401087</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1471,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129671473</v>
+        <v>129671474</v>
       </c>
       <c r="B10" t="n">
-        <v>97419</v>
+        <v>97733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1506,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>362642</v>
+        <v>362557</v>
       </c>
       <c r="R10" t="n">
-        <v>6401087</v>
+        <v>6401036</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1568,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129671460</v>
+        <v>129671475</v>
       </c>
       <c r="B11" t="n">
-        <v>96034</v>
+        <v>97733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>362627</v>
+        <v>362517</v>
       </c>
       <c r="R11" t="n">
-        <v>6401086</v>
+        <v>6401013</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1665,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129671470</v>
+        <v>129671476</v>
       </c>
       <c r="B12" t="n">
-        <v>97419</v>
+        <v>97733</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1700,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>362943</v>
+        <v>362557</v>
       </c>
       <c r="R12" t="n">
-        <v>6401326</v>
+        <v>6401084</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1762,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129671454</v>
+        <v>129671477</v>
       </c>
       <c r="B13" t="n">
-        <v>96034</v>
+        <v>97733</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1773,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1797,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>362976</v>
+        <v>362571</v>
       </c>
       <c r="R13" t="n">
-        <v>6401459</v>
+        <v>6401074</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1859,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129671488</v>
+        <v>129614106</v>
       </c>
       <c r="B14" t="n">
-        <v>97080</v>
+        <v>97394</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1888,19 +1868,23 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gesebol, Vg</t>
+          <t>Mjögasjön, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>362944</v>
+        <v>362800</v>
       </c>
       <c r="R14" t="n">
-        <v>6401327</v>
+        <v>6401256</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1924,12 +1908,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1 låga med kornknutmossa</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1944,22 +1943,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Tobias Federsel</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Tobias Federsel</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129671455</v>
+        <v>129671487</v>
       </c>
       <c r="B15" t="n">
-        <v>96034</v>
+        <v>97394</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1966,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>362956</v>
+        <v>362989</v>
       </c>
       <c r="R15" t="n">
-        <v>6401313</v>
+        <v>6401348</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2053,10 +2052,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129671467</v>
+        <v>129671488</v>
       </c>
       <c r="B16" t="n">
-        <v>97419</v>
+        <v>97394</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,21 +2063,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2569</v>
+        <v>2590</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>362965</v>
+        <v>362944</v>
       </c>
       <c r="R16" t="n">
-        <v>6401425</v>
+        <v>6401327</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2150,10 +2149,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129671458</v>
+        <v>129671489</v>
       </c>
       <c r="B17" t="n">
-        <v>96034</v>
+        <v>97394</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2161,21 +2160,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2185,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>362492</v>
+        <v>362800</v>
       </c>
       <c r="R17" t="n">
-        <v>6400983</v>
+        <v>6401187</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2247,10 +2246,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129671489</v>
+        <v>129671490</v>
       </c>
       <c r="B18" t="n">
-        <v>97080</v>
+        <v>97394</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2282,10 +2281,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>362800</v>
+        <v>362834</v>
       </c>
       <c r="R18" t="n">
-        <v>6401187</v>
+        <v>6401233</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2326,6 +2325,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129671468</v>
+        <v>129671454</v>
       </c>
       <c r="B19" t="n">
-        <v>97419</v>
+        <v>96348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>362966</v>
+        <v>362976</v>
       </c>
       <c r="R19" t="n">
-        <v>6401361</v>
+        <v>6401459</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129671476</v>
+        <v>129671455</v>
       </c>
       <c r="B20" t="n">
-        <v>97419</v>
+        <v>96348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>362557</v>
+        <v>362956</v>
       </c>
       <c r="R20" t="n">
-        <v>6401084</v>
+        <v>6401313</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2538,10 +2538,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129671477</v>
+        <v>129671456</v>
       </c>
       <c r="B21" t="n">
-        <v>97419</v>
+        <v>96348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2549,21 +2549,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>362571</v>
+        <v>362809</v>
       </c>
       <c r="R21" t="n">
-        <v>6401074</v>
+        <v>6401252</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2635,10 +2635,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129671501</v>
+        <v>129671457</v>
       </c>
       <c r="B22" t="n">
-        <v>96394</v>
+        <v>96348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2646,21 +2646,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>362633</v>
+        <v>362754</v>
       </c>
       <c r="R22" t="n">
-        <v>6401090</v>
+        <v>6401209</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129671456</v>
+        <v>129671458</v>
       </c>
       <c r="B23" t="n">
-        <v>96034</v>
+        <v>96348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>362809</v>
+        <v>362492</v>
       </c>
       <c r="R23" t="n">
-        <v>6401252</v>
+        <v>6400983</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2832,7 +2832,7 @@
         <v>129671459</v>
       </c>
       <c r="B24" t="n">
-        <v>96034</v>
+        <v>96348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129671487</v>
+        <v>129671460</v>
       </c>
       <c r="B25" t="n">
-        <v>97080</v>
+        <v>96348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2937,21 +2937,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>362989</v>
+        <v>362627</v>
       </c>
       <c r="R25" t="n">
-        <v>6401348</v>
+        <v>6401086</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3023,10 +3023,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129671474</v>
+        <v>129745963</v>
       </c>
       <c r="B26" t="n">
-        <v>97419</v>
+        <v>56925</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3034,37 +3034,49 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2569</v>
+        <v>100045</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gesebol, Vg</t>
+          <t>Gesebol 2:2, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>362557</v>
+        <v>362701</v>
       </c>
       <c r="R26" t="n">
-        <v>6401036</v>
+        <v>6401152</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3088,12 +3100,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3108,22 +3130,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Bo Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Bo Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129745963</v>
+        <v>129745850</v>
       </c>
       <c r="B27" t="n">
-        <v>56713</v>
+        <v>57141</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3131,33 +3153,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100045</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>sträckande SV</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3202,7 +3228,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3212,7 +3238,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3239,10 +3265,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129745850</v>
+        <v>129671481</v>
       </c>
       <c r="B28" t="n">
-        <v>57073</v>
+        <v>97983</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3250,53 +3276,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gesebol 2:2, Vg</t>
+          <t>Gesebol, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>362701</v>
+        <v>362639</v>
       </c>
       <c r="R28" t="n">
-        <v>6401152</v>
+        <v>6401070</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3320,22 +3330,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:03</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>10:03</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3350,12 +3350,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bo Hultgren</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bo Hultgren</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 52087-2025 artfynd.xlsx
+++ b/artfynd/A 52087-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671501</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671467</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671468</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671469</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671470</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671471</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671472</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671473</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671474</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671475</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671476</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671477</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1952,6 +2017,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129614106</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2049,6 +2119,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671487</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2146,6 +2221,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671488</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2243,6 +2323,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671489</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2341,6 +2426,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671490</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2438,6 +2528,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671454</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2535,6 +2630,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671455</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2632,6 +2732,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671456</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2729,6 +2834,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671457</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2826,6 +2936,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671458</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2923,6 +3038,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671459</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3020,6 +3140,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671460</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3139,6 +3264,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129745963</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3262,6 +3392,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129745850</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3359,8 +3494,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671481</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>